--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486503_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486503_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.227499999999999</v>
+        <v>8.2776</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4475</v>
+        <v>4.7532</v>
       </c>
       <c r="F2" t="n">
-        <v>5.78</v>
+        <v>3.5244</v>
       </c>
       <c r="G2" t="n">
-        <v>5.8731</v>
+        <v>5.1739</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2762</v>
+        <v>2.4207</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5969</v>
+        <v>2.7532</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8277</v>
+        <v>3.1906</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8715</v>
+        <v>0.949</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9562</v>
+        <v>2.2416</v>
       </c>
       <c r="M2" t="n">
-        <v>2.0454</v>
+        <v>1.9833</v>
       </c>
       <c r="N2" t="n">
-        <v>1.4047</v>
+        <v>1.4717</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6407</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6372</v>
+        <v>0.6687</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8172</v>
+        <v>0.4326</v>
       </c>
       <c r="U2" t="n">
-        <v>0.82</v>
+        <v>0.2361</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9347</v>
+        <v>1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.9925</v>
+        <v>7.9308</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5297</v>
+        <v>2.3358</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4628</v>
+        <v>5.5951</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1739</v>
+        <v>5.8731</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4207</v>
+        <v>4.2762</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7532</v>
+        <v>1.5969</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1906</v>
+        <v>3.8277</v>
       </c>
       <c r="K3" t="n">
-        <v>0.949</v>
+        <v>2.8715</v>
       </c>
       <c r="L3" t="n">
-        <v>2.2416</v>
+        <v>0.9562</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9833</v>
+        <v>2.0454</v>
       </c>
       <c r="N3" t="n">
-        <v>1.4717</v>
+        <v>1.4047</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.6407</v>
       </c>
       <c r="P3" t="n">
-        <v>1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R3" t="n">
-        <v>1.305</v>
+        <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3836</v>
+        <v>1.3405</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2091</v>
+        <v>0.7054</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1745</v>
+        <v>0.6351</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>0.9347</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BARCELLO</t>
+          <t>D. DE SOUSA ANJO BRITO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.8993</v>
+        <v>7.0155</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3.5238</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8993</v>
+        <v>3.4918</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5533</v>
+        <v>4.5824</v>
       </c>
       <c r="H4" t="n">
-        <v>3.087</v>
+        <v>2.0803</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4663</v>
+        <v>2.5022</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>3.334</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7588</v>
+        <v>2.0685</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7412</v>
+        <v>1.2655</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0533</v>
+        <v>1.2485</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3282</v>
+        <v>0.0118</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7251</v>
+        <v>1.2367</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.305</v>
+        <v>-2.3926</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0875</v>
+        <v>2.8276</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1731</v>
+        <v>0.3031</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4146</v>
+        <v>0.6922</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7585</v>
+        <v>-0.3891</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3904</v>
+        <v>1.695</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3904</v>
+        <v>1.8902</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. DE SOUSA ANJO BRITO</t>
+          <t>A. BARCELLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.6628</v>
+        <v>6.961</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3868</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>3.276</v>
+        <v>2.961</v>
       </c>
       <c r="G5" t="n">
-        <v>4.5824</v>
+        <v>5.5533</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0803</v>
+        <v>3.087</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5022</v>
+        <v>2.4663</v>
       </c>
       <c r="J5" t="n">
-        <v>3.334</v>
+        <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0685</v>
+        <v>2.7588</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2655</v>
+        <v>1.7412</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2485</v>
+        <v>1.0533</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0118</v>
+        <v>0.3282</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2367</v>
+        <v>0.7251</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3926</v>
+        <v>-1.305</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8276</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0496</v>
+        <v>1.2347</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5552</v>
+        <v>0.4146</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6048</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>1.695</v>
+        <v>0.3904</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8902</v>
+        <v>0.3904</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5936</v>
+        <v>4.8093</v>
       </c>
       <c r="E6" t="n">
         <v>1.6405</v>
       </c>
       <c r="F6" t="n">
-        <v>2.953</v>
+        <v>3.1688</v>
       </c>
       <c r="G6" t="n">
         <v>3.7407</v>
@@ -922,13 +922,13 @@
         <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6353</v>
+        <v>0.8511</v>
       </c>
       <c r="T6" t="n">
         <v>0.5396</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0958</v>
+        <v>0.3115</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4441</v>
+        <v>3.7601</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7778</v>
+        <v>1.0014</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6662</v>
+        <v>2.7587</v>
       </c>
       <c r="G7" t="n">
         <v>1.9966</v>
@@ -1000,13 +1000,13 @@
         <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8151</v>
+        <v>1.1311</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4146</v>
+        <v>0.6381</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4005</v>
+        <v>0.493</v>
       </c>
       <c r="V7" t="n">
         <v>-1.3252</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0455</v>
+        <v>0.8627</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.449</v>
+        <v>-1.2003</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4945</v>
+        <v>2.063</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7818000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3047</v>
+        <v>0.122</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0769</v>
+        <v>0.1719</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3816</v>
+        <v>-0.0499</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7379</v>
+        <v>0.8441</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0851</v>
+        <v>0.0519</v>
       </c>
       <c r="F9" t="n">
-        <v>0.823</v>
+        <v>0.7922</v>
       </c>
       <c r="G9" t="n">
         <v>1.4453</v>
@@ -1156,13 +1156,13 @@
         <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2501</v>
+        <v>-0.1439</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3425</v>
+        <v>-0.2055</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0924</v>
+        <v>0.0616</v>
       </c>
       <c r="V9" t="n">
         <v>0.1952</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ETXEGUREN GONZALEZ</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1266</v>
+        <v>0.5678</v>
       </c>
       <c r="E10" t="n">
-        <v>0.062</v>
+        <v>-0.4819</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0645</v>
+        <v>1.0497</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1519</v>
+        <v>0.4249</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.3222</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7451</v>
+        <v>0.1028</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0547</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0547</v>
+        <v>0.1095</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.7068</v>
       </c>
       <c r="M10" t="n">
-        <v>0.09710000000000001</v>
+        <v>1.0222</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6479</v>
+        <v>0.2127</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7451</v>
+        <v>0.8096</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2569</v>
+        <v>-0.3797</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5516</v>
+        <v>0.1154</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2947</v>
+        <v>-0.4951</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9347</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.5443</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3904</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>A. ETXEGUREN GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.07240000000000001</v>
+        <v>-0.0468</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7307</v>
+        <v>-0.0497</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8031</v>
+        <v>0.0029</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4249</v>
+        <v>0.1519</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3222</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1028</v>
+        <v>0.7451</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5973000000000001</v>
+        <v>0.0547</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1095</v>
+        <v>0.0547</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7068</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.0222</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2127</v>
+        <v>-0.6479</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8096</v>
+        <v>0.7451</v>
       </c>
       <c r="P11" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8751</v>
+        <v>0.0835</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1334</v>
+        <v>0.4398</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7417</v>
+        <v>-0.3563</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.9347</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.5443</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5226</v>
+        <v>-0.4301</v>
       </c>
       <c r="E12" t="n">
         <v>-0.8838</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3612</v>
+        <v>0.4537</v>
       </c>
       <c r="G12" t="n">
         <v>0.1368</v>
@@ -1390,13 +1390,13 @@
         <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2107</v>
+        <v>0.3031</v>
       </c>
       <c r="T12" t="n">
         <v>0.149</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0616</v>
+        <v>0.1541</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.8638</v>
+        <v>-7.4512</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.7185</v>
+        <v>-7.0285</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1452</v>
+        <v>-0.4227</v>
       </c>
       <c r="G13" t="n">
         <v>-4.0644</v>
@@ -1468,13 +1468,13 @@
         <v>1.305</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3306</v>
+        <v>-0.2569</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5432</v>
+        <v>0.2331</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2126</v>
+        <v>-0.49</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2599</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>32.41580000000001</v>
+        <v>33.1008</v>
       </c>
       <c r="E14" t="n">
-        <v>6.977199999999999</v>
+        <v>7.662400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>25.4384</v>
+        <v>25.4386</v>
       </c>
       <c r="G14" t="n">
         <v>24.2327</v>
@@ -1546,13 +1546,13 @@
         <v>16.3129</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5724</v>
+        <v>5.2573</v>
       </c>
       <c r="T14" t="n">
-        <v>3.6413</v>
+        <v>4.3262</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9311000000000001</v>
+        <v>0.9311000000000003</v>
       </c>
       <c r="V14" t="n">
         <v>-0.7394999999999996</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. VUCETIC</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0419</v>
+        <v>2.0093</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2677</v>
+        <v>0.219</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3096</v>
+        <v>1.7903</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0403</v>
+        <v>0.4171</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4842</v>
+        <v>-0.8331</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4439</v>
+        <v>1.2503</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6156</v>
+        <v>-0.7876</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6538</v>
+        <v>-0.4832</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0382</v>
+        <v>-0.3044</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5752</v>
+        <v>1.2047</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8304</v>
+        <v>-0.3499</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4056</v>
+        <v>1.5546</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1475</v>
+        <v>0.3746</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2402</v>
+        <v>0.2464</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0927</v>
+        <v>0.1283</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9347</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1952</v>
+        <v>0.7602</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7395</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>V. VUCETIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9412</v>
+        <v>1.6386</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3307</v>
+        <v>-0.9383</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6105</v>
+        <v>2.5768</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4171</v>
+        <v>-0.0403</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8331</v>
+        <v>-1.4842</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2503</v>
+        <v>1.4439</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7876</v>
+        <v>-0.6156</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4832</v>
+        <v>-0.6538</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3044</v>
+        <v>0.0382</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2047</v>
+        <v>0.5752</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3499</v>
+        <v>-0.8304</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5546</v>
+        <v>1.4056</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3066</v>
+        <v>0.7442</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3581</v>
+        <v>0.5696</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0516</v>
+        <v>0.1745</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.9347</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7602</v>
+        <v>0.1952</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1952</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3145</v>
+        <v>0.3573</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7854</v>
+        <v>-0.2267</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4709</v>
+        <v>0.584</v>
       </c>
       <c r="G17" t="n">
         <v>-1.4646</v>
@@ -1780,13 +1780,13 @@
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8924</v>
+        <v>-0.2205</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0839</v>
+        <v>-0.5251</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1915</v>
+        <v>0.3046</v>
       </c>
       <c r="V17" t="n">
         <v>2.2599</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ BARRIENTOS</t>
+          <t>M. HERON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.265</v>
+        <v>-0.9153</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5759</v>
+        <v>-3.9925</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.841</v>
+        <v>3.0771</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.536</v>
+        <v>0.0398</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0189</v>
+        <v>-0.9307</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4829</v>
+        <v>0.9706</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3789</v>
+        <v>-1.9944</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1095</v>
+        <v>-0.5808</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2694</v>
+        <v>-1.4136</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9149</v>
+        <v>2.0343</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1284</v>
+        <v>-0.3499</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2136</v>
+        <v>2.3842</v>
       </c>
       <c r="P18" t="n">
-        <v>0.87</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R18" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2912</v>
+        <v>0.0454</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1971</v>
+        <v>0.1346</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0941</v>
+        <v>-0.0892</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8902</v>
+        <v>0.7395</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.8902</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8498</v>
+        <v>-1.0265</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1416</v>
+        <v>0.1936</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7082</v>
+        <v>-1.2201</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0501</v>
@@ -1936,13 +1936,13 @@
         <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7519</v>
+        <v>-0.9286</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2209</v>
+        <v>-0.8856000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.531</v>
+        <v>-0.043</v>
       </c>
       <c r="V19" t="n">
         <v>0.0822</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9887</v>
+        <v>-1.2874</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2369</v>
+        <v>-1.5663</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2481</v>
+        <v>0.279</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8483</v>
@@ -2014,13 +2014,13 @@
         <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.793</v>
+        <v>-0.0916</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.113</v>
+        <v>0.5576</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.68</v>
+        <v>-0.6492</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. HERON</t>
+          <t>M. RODRIGUEZ BARRIENTOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1356</v>
+        <v>-1.7788</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.663</v>
+        <v>0.1289</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5274</v>
+        <v>-1.9077</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0398</v>
+        <v>-0.536</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9307</v>
+        <v>-1.0189</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9706</v>
+        <v>0.4829</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.9944</v>
+        <v>0.3789</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5808</v>
+        <v>0.1095</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4136</v>
+        <v>0.2694</v>
       </c>
       <c r="M21" t="n">
-        <v>2.0343</v>
+        <v>-0.9149</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3499</v>
+        <v>-1.1284</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3842</v>
+        <v>0.2136</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1749</v>
+        <v>-0.2226</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.536</v>
+        <v>-0.2499</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6389</v>
+        <v>0.0273</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7395</v>
+        <v>-1.8902</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3904</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>I. JAKOVICS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0242</v>
+        <v>-4.2174</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7183</v>
+        <v>-2.3142</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3059</v>
+        <v>-1.9033</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3127</v>
+        <v>-4.0722</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.7796</v>
+        <v>0.8547</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5331</v>
+        <v>-4.9269</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.993</v>
+        <v>-1.1245</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.0313</v>
+        <v>2.0836</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0382</v>
+        <v>-3.2081</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3197</v>
+        <v>-2.9477</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7484</v>
+        <v>-1.2289</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5714</v>
+        <v>-1.7188</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0535</v>
+        <v>-0.837</v>
       </c>
       <c r="T22" t="n">
-        <v>2.1018</v>
+        <v>-0.1021</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0482</v>
+        <v>-0.7348</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.9825</v>
+        <v>0.2568</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.243</v>
+        <v>0.2568</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. JAKOVICS</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9612</v>
+        <v>-5.4075</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.873</v>
+        <v>-2.8248</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0882</v>
+        <v>-2.5827</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.0722</v>
+        <v>-3.3781</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8547</v>
+        <v>-2.1804</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.9269</v>
+        <v>-1.1977</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1245</v>
+        <v>-0.2304</v>
       </c>
       <c r="K23" t="n">
-        <v>2.0836</v>
+        <v>-1.283</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.2081</v>
+        <v>1.0527</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9477</v>
+        <v>-3.1477</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2289</v>
+        <v>-0.8974</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7188</v>
+        <v>-2.2504</v>
       </c>
       <c r="P23" t="n">
-        <v>0.435</v>
+        <v>-1.305</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5807</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6609</v>
+        <v>-0.4194</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9198</v>
+        <v>-0.192</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2568</v>
+        <v>-0.113</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.2568</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6028</v>
+        <v>-5.4848</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2718</v>
+        <v>-3.3946</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.331</v>
+        <v>-2.0902</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3781</v>
+        <v>-3.3127</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.1804</v>
+        <v>-2.7796</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1977</v>
+        <v>-0.5331</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2304</v>
+        <v>-1.993</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.283</v>
+        <v>-2.0313</v>
       </c>
       <c r="L24" t="n">
-        <v>1.0527</v>
+        <v>0.0382</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.1477</v>
+        <v>-1.3197</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8974</v>
+        <v>-0.7484</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.2504</v>
+        <v>-0.5714</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R24" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8067</v>
+        <v>-0.4071</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8663999999999999</v>
+        <v>0.4254</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0597</v>
+        <v>-0.8325</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.113</v>
+        <v>-1.9825</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.113</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.3586</v>
+        <v>-6.1286</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.5249</v>
+        <v>-4.4131</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8337</v>
+        <v>-1.7155</v>
       </c>
       <c r="G25" t="n">
         <v>-2.4572</v>
@@ -2404,13 +2404,13 @@
         <v>0.2175</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6611</v>
+        <v>-0.4311</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.5732</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0239</v>
+        <v>0.1421</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1952</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.8984</v>
+        <v>-8.6845</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.8626</v>
+        <v>-6.3096</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.0358</v>
+        <v>-2.3749</v>
       </c>
       <c r="G26" t="n">
         <v>-6.5301</v>
@@ -2482,13 +2482,13 @@
         <v>1.5225</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2895</v>
+        <v>-0.4966</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3377</v>
+        <v>-0.1093</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0482</v>
+        <v>-0.3873</v>
       </c>
       <c r="V26" t="n">
         <v>0.0822</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-32.4157</v>
+        <v>-30.9256</v>
       </c>
       <c r="E27" t="n">
         <v>-25.4386</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.9773</v>
+        <v>-5.4872</v>
       </c>
       <c r="G27" t="n">
         <v>-24.2327</v>
@@ -2530,7 +2530,7 @@
         <v>-16.4831</v>
       </c>
       <c r="I27" t="n">
-        <v>-7.7493</v>
+        <v>-7.749300000000002</v>
       </c>
       <c r="J27" t="n">
         <v>-12.1905</v>
@@ -2551,7 +2551,7 @@
         <v>-1.2433</v>
       </c>
       <c r="P27" t="n">
-        <v>-4.3503</v>
+        <v>-4.350300000000001</v>
       </c>
       <c r="Q27" t="n">
         <v>-16.3129</v>
@@ -2560,16 +2560,16 @@
         <v>11.9625</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.5724</v>
+        <v>-3.082299999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9312000000000004</v>
+        <v>-0.9309999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.6412</v>
+        <v>-2.1512</v>
       </c>
       <c r="V27" t="n">
-        <v>0.7393999999999998</v>
+        <v>0.7394000000000003</v>
       </c>
       <c r="W27" t="n">
         <v>3.9962</v>
